--- a/Configs/Datas/__beans__.xlsx
+++ b/Configs/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B9DB6F-C76D-41E3-A0F9-379FDD5B7A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7ADA46-E06F-45A0-AFD2-03FC6788D8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -270,6 +270,106 @@
   </si>
   <si>
     <t>受击反馈类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.BuffEffectData</t>
+  </si>
+  <si>
+    <t>Buff数据基类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger_event</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.BuffEffectType</t>
+  </si>
+  <si>
+    <t>ZZZ.BuffTriggerEvent</t>
+  </si>
+  <si>
+    <t>ZZZ.AttributeId</t>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>布尔参数 1,是否随层数倍增 / 是否平滑缓出恢复</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串参数 1,视效音效寻址 Key / 关联触发的子 BuffID / 标签</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点参数 2,跳字间隔（DoT 间隔 0.5s）/ 子弹时间持续 (0.8s)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点参数 1,数值大小（如增伤 0.2）/ 子弹时间流速 (0.1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>整型参数 1,属性修改运算类型（0=Flat, 1=Percent）/ 优先级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>作用属性 ID,属性加成时使用（如 ATK, BaseResilience）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件监听时机,声明何时触发（常驻效果填 None）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果类型枚举,路由创建具体的逻辑执行器</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>param_int1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>param_float2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>param_float1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>param_bool1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>param_str1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.ActionResilience</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作打断力与抗打断韧性</t>
+  </si>
+  <si>
+    <t>interrupt_level</t>
+  </si>
+  <si>
+    <t>resilience_bonus</t>
+  </si>
+  <si>
+    <t>动作持续期间获得的额外抗打断韧性加成（0=常规轻攻击，50=霸体/重攻击）</t>
+  </si>
+  <si>
+    <t>动作附带打断等级（0=不可打断，1=常规轻击，5=招架弹刀，10=强力爆发，999=绝对打断）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -277,7 +377,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +442,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF292929"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -383,7 +490,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -402,10 +509,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -685,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.625" customWidth="1"/>
@@ -727,15 +837,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -885,7 +995,7 @@
       <c r="L11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1024,6 +1134,134 @@
       </c>
       <c r="N21" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" t="s">
+        <v>78</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J31" t="s">
+        <v>99</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N31" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
